--- a/etf_holdings/2026-09-29_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:44</t>
+          <t>2026-09-29 01:00:50</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:44</t>
+          <t>2026-09-29 01:00:50</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:44</t>
+          <t>2026-09-29 01:00:50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:44</t>
+          <t>2026-09-29 01:00:50</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:44</t>
+          <t>2026-09-29 01:00:50</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:44</t>
+          <t>2026-09-29 01:00:50</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:44</t>
+          <t>2026-09-29 01:00:50</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:44</t>
+          <t>2026-09-29 01:00:50</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:44</t>
+          <t>2026-09-29 01:00:50</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:44</t>
+          <t>2026-09-29 01:00:50</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:44</t>
+          <t>2026-09-29 01:00:50</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:44</t>
+          <t>2026-09-29 01:00:50</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:44</t>
+          <t>2026-09-29 01:00:50</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:44</t>
+          <t>2026-09-29 01:00:50</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:44</t>
+          <t>2026-09-29 01:00:50</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:45</t>
+          <t>2026-09-29 01:00:52</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:45</t>
+          <t>2026-09-29 01:00:52</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:45</t>
+          <t>2026-09-29 01:00:52</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:45</t>
+          <t>2026-09-29 01:00:52</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:45</t>
+          <t>2026-09-29 01:00:52</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:45</t>
+          <t>2026-09-29 01:00:52</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:45</t>
+          <t>2026-09-29 01:00:52</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:45</t>
+          <t>2026-09-29 01:00:52</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:45</t>
+          <t>2026-09-29 01:00:52</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:45</t>
+          <t>2026-09-29 01:00:52</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:45</t>
+          <t>2026-09-29 01:00:52</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:45</t>
+          <t>2026-09-29 01:00:52</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:45</t>
+          <t>2026-09-29 01:00:52</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:45</t>
+          <t>2026-09-29 01:00:52</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:45</t>
+          <t>2026-09-29 01:00:52</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:46</t>
+          <t>2026-09-29 01:00:53</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:46</t>
+          <t>2026-09-29 01:00:53</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:46</t>
+          <t>2026-09-29 01:00:53</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:46</t>
+          <t>2026-09-29 01:00:53</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:46</t>
+          <t>2026-09-29 01:00:53</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:46</t>
+          <t>2026-09-29 01:00:53</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:46</t>
+          <t>2026-09-29 01:00:53</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:46</t>
+          <t>2026-09-29 01:00:53</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:46</t>
+          <t>2026-09-29 01:00:53</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:46</t>
+          <t>2026-09-29 01:00:53</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:46</t>
+          <t>2026-09-29 01:00:53</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:46</t>
+          <t>2026-09-29 01:00:53</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:46</t>
+          <t>2026-09-29 01:00:53</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:46</t>
+          <t>2026-09-29 01:00:53</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:46</t>
+          <t>2026-09-29 01:00:53</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:47</t>
+          <t>2026-09-29 01:00:54</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:47</t>
+          <t>2026-09-29 01:00:54</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:47</t>
+          <t>2026-09-29 01:00:54</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:47</t>
+          <t>2026-09-29 01:00:54</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:47</t>
+          <t>2026-09-29 01:00:54</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-29_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:50</t>
+          <t>2026-09-29 01:39:38</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:50</t>
+          <t>2026-09-29 01:39:38</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:50</t>
+          <t>2026-09-29 01:39:38</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:50</t>
+          <t>2026-09-29 01:39:38</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:50</t>
+          <t>2026-09-29 01:39:38</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:50</t>
+          <t>2026-09-29 01:39:38</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:50</t>
+          <t>2026-09-29 01:39:38</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:50</t>
+          <t>2026-09-29 01:39:38</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:50</t>
+          <t>2026-09-29 01:39:38</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:50</t>
+          <t>2026-09-29 01:39:38</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:50</t>
+          <t>2026-09-29 01:39:38</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:50</t>
+          <t>2026-09-29 01:39:38</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:50</t>
+          <t>2026-09-29 01:39:38</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:50</t>
+          <t>2026-09-29 01:39:38</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:50</t>
+          <t>2026-09-29 01:39:38</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:52</t>
+          <t>2026-09-29 01:39:39</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:52</t>
+          <t>2026-09-29 01:39:39</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:52</t>
+          <t>2026-09-29 01:39:39</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:52</t>
+          <t>2026-09-29 01:39:39</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:52</t>
+          <t>2026-09-29 01:39:39</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:52</t>
+          <t>2026-09-29 01:39:39</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:52</t>
+          <t>2026-09-29 01:39:39</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:52</t>
+          <t>2026-09-29 01:39:39</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:52</t>
+          <t>2026-09-29 01:39:39</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:52</t>
+          <t>2026-09-29 01:39:39</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:52</t>
+          <t>2026-09-29 01:39:39</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:52</t>
+          <t>2026-09-29 01:39:39</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:52</t>
+          <t>2026-09-29 01:39:39</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:52</t>
+          <t>2026-09-29 01:39:39</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:52</t>
+          <t>2026-09-29 01:39:39</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:53</t>
+          <t>2026-09-29 01:39:40</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:53</t>
+          <t>2026-09-29 01:39:40</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:53</t>
+          <t>2026-09-29 01:39:40</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:53</t>
+          <t>2026-09-29 01:39:40</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:53</t>
+          <t>2026-09-29 01:39:40</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:53</t>
+          <t>2026-09-29 01:39:40</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:53</t>
+          <t>2026-09-29 01:39:40</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:53</t>
+          <t>2026-09-29 01:39:40</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:53</t>
+          <t>2026-09-29 01:39:40</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:53</t>
+          <t>2026-09-29 01:39:40</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:53</t>
+          <t>2026-09-29 01:39:40</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:53</t>
+          <t>2026-09-29 01:39:40</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:53</t>
+          <t>2026-09-29 01:39:40</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:53</t>
+          <t>2026-09-29 01:39:40</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:53</t>
+          <t>2026-09-29 01:39:40</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:54</t>
+          <t>2026-09-29 01:39:41</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:54</t>
+          <t>2026-09-29 01:39:41</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:54</t>
+          <t>2026-09-29 01:39:41</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:54</t>
+          <t>2026-09-29 01:39:41</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:54</t>
+          <t>2026-09-29 01:39:41</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-29_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:38</t>
+          <t>2026-09-29 22:54:48</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,12 +509,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-1%2475</t>
+          <t>0%2475</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -522,12 +522,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9.32%753,000</t>
+          <t>9.23%753,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9.32%</t>
+          <t>9.23%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:38</t>
+          <t>2026-09-29 22:54:48</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+1.93%5285</t>
+          <t>-7.1%4910</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+1.93%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5285</v>
+        <v>4910</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.39%249,000</t>
+          <t>6.52%249,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.39%</t>
+          <t>6.52%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.50%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:38</t>
+          <t>2026-09-29 22:54:48</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.32%12350</t>
+          <t>-1.9%12115</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>-1.9%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>12350</v>
+        <v>12115</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4.11%67,000</t>
+          <t>4.10%67,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.11%</t>
+          <t>4.10%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:38</t>
+          <t>2026-09-29 22:54:48</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+0.53%1910</t>
+          <t>-3.93%1835</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>-3.93%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1910</v>
+        <v>1835</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3.80%404,000</t>
+          <t>3.82%404,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3.80%</t>
+          <t>3.82%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:38</t>
+          <t>2026-09-29 22:54:48</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+2.16%1185</t>
+          <t>-1.69%1165</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+2.16%</t>
+          <t>-1.69%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1185</v>
+        <v>1165</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.40%591,000</t>
+          <t>3.47%591,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3.40%</t>
+          <t>3.47%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:38</t>
+          <t>2026-09-29 22:54:48</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+0.6%5050</t>
+          <t>-2.57%4920</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+0.6%</t>
+          <t>-2.57%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>5050</v>
+        <v>4920</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.38%136,000</t>
+          <t>3.40%136,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.38%</t>
+          <t>3.40%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:38</t>
+          <t>2026-09-29 22:54:48</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2408南亞科</t>
+          <t>1303南亞</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-2.33%503</t>
+          <t>+3.78%247</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-2.33%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>503</v>
+        <v>247</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2.80%1,096,000</t>
+          <t>2.85%2,416,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2.80%</t>
+          <t>2.85%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1096000</v>
+        <v>2416000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:38</t>
+          <t>2026-09-29 22:54:48</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1303南亞</t>
+          <t>2408南亞科</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+4.62%238</t>
+          <t>+0.6%506</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+4.62%</t>
+          <t>+0.6%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>238</v>
+        <v>506</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.72%2,416,000</t>
+          <t>2.73%1,096,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2.72%</t>
+          <t>2.73%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2416000</v>
+        <v>1096000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:38</t>
+          <t>2026-09-29 22:54:48</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+1.67%8525</t>
+          <t>-7.04%7925</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+1.67%</t>
+          <t>-7.04%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>8525</v>
+        <v>7925</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.45%59,000</t>
+          <t>2.49%59,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.45%</t>
+          <t>2.49%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:38</t>
+          <t>2026-09-29 22:54:48</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,12 +1058,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-2.15%250.5</t>
+          <t>0%250.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-2.15%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.44%1,921,000</t>
+          <t>2.38%1,921,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.38%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:38</t>
+          <t>2026-09-29 22:54:48</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+2.45%3555</t>
+          <t>-0.36%6895</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+2.45%</t>
+          <t>-0.36%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>3555</v>
+        <v>6895</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.30%134,000</t>
+          <t>2.36%69,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>2.36%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>134000</v>
+        <v>69000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:38</t>
+          <t>2026-09-29 22:54:48</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2368金像電</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-3.07%1105</t>
+          <t>-4.36%3400</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-3.07%</t>
+          <t>-4.36%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1105</v>
+        <v>3400</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.22%393,000</t>
+          <t>2.36%134,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>2.36%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>393000</v>
+        <v>134000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:38</t>
+          <t>2026-09-29 22:54:48</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+7.96%6920</t>
+          <t>-1.72%687</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+7.96%</t>
+          <t>-1.72%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>6920</v>
+        <v>687</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.19%69,000</t>
+          <t>2.15%621,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.19%</t>
+          <t>2.15%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>69000</v>
+        <v>621000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:38</t>
+          <t>2026-09-29 22:54:48</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>7769鴻勁</t>
+          <t>2368金像電</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-5.1%5670</t>
+          <t>+1.36%1120</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>+1.36%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5670</v>
+        <v>1120</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.16%73,000</t>
+          <t>2.15%393,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.16%</t>
+          <t>2.15%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>73000</v>
+        <v>393000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:38</t>
+          <t>2026-09-29 22:54:48</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>7769鴻勁</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+0.87%699</t>
+          <t>-1.5%5585</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+0.87%</t>
+          <t>-1.5%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>699</v>
+        <v>5585</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.13%621,000</t>
+          <t>2.05%73,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>2.05%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>621000</v>
+        <v>73000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:39</t>
+          <t>2026-09-29 22:54:49</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,25 +1424,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-2.19%19835</t>
+          <t>-2.22%19395</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.22%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>19835</v>
+        <v>19395</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.04%20,300</t>
+          <t>1.99%20,300</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>1.99%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:39</t>
+          <t>2026-09-29 22:54:49</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,25 +1485,25 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-0.58%171.5</t>
+          <t>+1.46%174</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-0.58%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>171.5</v>
+        <v>174</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.96%2,293,000</t>
+          <t>1.95%2,293,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>1.95%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:39</t>
+          <t>2026-09-29 22:54:49</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-3.65%5415</t>
+          <t>-0.67%1485</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-3.65%</t>
+          <t>-0.67%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5415</v>
+        <v>1485</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.84%66,000</t>
+          <t>1.78%240,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.78%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>66000</v>
+        <v>240000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:39</t>
+          <t>2026-09-29 22:54:49</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,34 +1602,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>8299群聯</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-4.06%2125</t>
+          <t>-4.25%5185</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-4.06%</t>
+          <t>-4.25%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2125</v>
+        <v>5185</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.84%168,000</t>
+          <t>1.77%66,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.77%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>168000</v>
+        <v>66000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:39</t>
+          <t>2026-09-29 22:54:49</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>8299群聯</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+2.4%1495</t>
+          <t>-0.47%2115</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+2.4%</t>
+          <t>-0.47%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1495</v>
+        <v>2115</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.74%240,000</t>
+          <t>1.77%168,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>1.77%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>240000</v>
+        <v>168000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:39</t>
+          <t>2026-09-29 22:54:49</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,25 +1729,25 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+0.75%2700</t>
+          <t>-1.85%2650</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+0.75%</t>
+          <t>-1.85%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2700</v>
+        <v>2650</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.71%128,600</t>
+          <t>1.72%128,600</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.72%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:39</t>
+          <t>2026-09-29 22:54:49</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,25 +1790,25 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-1.29%2295</t>
+          <t>-4.79%2185</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-4.79%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2295</v>
+        <v>2185</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.70%148,000</t>
+          <t>1.68%148,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.68%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:39</t>
+          <t>2026-09-29 22:54:49</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,25 +1851,25 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-0.88%338.5</t>
+          <t>-0.59%336.5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>338.5</v>
+        <v>336.5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.67%987,000</t>
+          <t>1.65%987,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.65%</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:39</t>
+          <t>2026-09-29 22:54:49</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,16 +1912,16 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+0.26%1895</t>
+          <t>-4.49%1810</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>-4.49%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1895</v>
+        <v>1810</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:39</t>
+          <t>2026-09-29 22:54:49</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>6515穎崴</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-2.42%5850</t>
+          <t>-0.71%2100</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>-0.71%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>5850</v>
+        <v>2100</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.63%55,000</t>
+          <t>1.62%155,105</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.62%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>55000</v>
+        <v>155105</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:39</t>
+          <t>2026-09-29 22:54:49</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>6515穎崴</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+0.48%2115</t>
+          <t>-2.99%5675</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>-2.99%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2115</v>
+        <v>5675</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.62%155,105</t>
+          <t>1.59%55,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.59%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>155105</v>
+        <v>55000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:39</t>
+          <t>2026-09-29 22:54:49</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,25 +2095,25 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+2.48%1240</t>
+          <t>+2.42%1270</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+2.48%</t>
+          <t>+2.42%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1240</v>
+        <v>1270</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.50%251,000</t>
+          <t>1.54%251,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.54%</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:39</t>
+          <t>2026-09-29 22:54:49</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,25 +2156,25 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+6.18%962</t>
+          <t>-0.73%955</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+6.18%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>962</v>
+        <v>955</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.45%323,000</t>
+          <t>1.54%323,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.54%</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:39</t>
+          <t>2026-09-29 22:54:49</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,16 +2217,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0%45.6</t>
+          <t>-1.54%44.9</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-1.54%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>45.6</v>
+        <v>44.9</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:39</t>
+          <t>2026-09-29 22:54:49</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2327國巨*</t>
+          <t>6213聯茂</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+1.22%580</t>
+          <t>+4.2%620</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+1.22%</t>
+          <t>+4.2%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>580</v>
+        <v>620</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.38%485,000</t>
+          <t>1.42%482,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.42%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>485000</v>
+        <v>482000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:40</t>
+          <t>2026-09-29 22:54:50</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>2327國巨*</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-0.65%1530</t>
+          <t>-5.52%548</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-0.65%</t>
+          <t>-5.52%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1530</v>
+        <v>548</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.38%181,000</t>
+          <t>1.39%485,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.39%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>181000</v>
+        <v>485000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:40</t>
+          <t>2026-09-29 22:54:50</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>6213聯茂</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+9.98%595</t>
+          <t>+3.59%1585</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+9.98%</t>
+          <t>+3.59%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>595</v>
+        <v>1585</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.29%482,000</t>
+          <t>1.37%181,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.37%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>482000</v>
+        <v>181000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:40</t>
+          <t>2026-09-29 22:54:50</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,25 +2461,25 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-0.58%68.5</t>
+          <t>+0.29%68.7</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-0.58%</t>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>68.5</v>
+        <v>68.7</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.26%3,699,000</t>
+          <t>1.25%3,699,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.25%</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:40</t>
+          <t>2026-09-29 22:54:50</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,25 +2522,25 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-0.96%361.5</t>
+          <t>+0.14%362</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-0.96%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>361.5</v>
+        <v>362</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.25%694,000</t>
+          <t>1.24%694,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:40</t>
+          <t>2026-09-29 22:54:50</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,34 +2578,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3036文曄</t>
+          <t>3231緯創</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+0.49%207</t>
+          <t>+0.54%185.5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+0.54%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>207</v>
+        <v>185.5</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.17%1,147,000</t>
+          <t>1.19%1,298,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>1147000</v>
+        <v>1298000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:40</t>
+          <t>2026-09-29 22:54:50</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,38 +2639,38 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3231緯創</t>
+          <t>3036文曄</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+2.5%184.5</t>
+          <t>+0.24%207.5</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+2.5%</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>184.5</v>
+        <v>207.5</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.16%1,298,000</t>
+          <t>1.18%1,147,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.18%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>1298000</v>
+        <v>1147000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:40</t>
+          <t>2026-09-29 22:54:50</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,34 +2700,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>5904寶雅*</t>
+          <t>3026禾伸堂</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-2.12%69.3</t>
+          <t>-1.73%796</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-2.12%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>69.3</v>
+        <v>796</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1.10%3,124,500</t>
+          <t>1.15%286,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.15%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>3124500</v>
+        <v>286000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:40</t>
+          <t>2026-09-29 22:54:50</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>3026禾伸堂</t>
+          <t>5904寶雅*</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+5.47%810</t>
+          <t>-0.72%68.8</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+5.47%</t>
+          <t>-0.72%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>810</v>
+        <v>68.8</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1.09%286,000</t>
+          <t>1.07%3,124,500</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.07%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>286000</v>
+        <v>3124500</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:40</t>
+          <t>2026-09-29 22:54:50</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3044健鼎</t>
+          <t>3293鈊象</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-0.92%538</t>
+          <t>+2.37%779</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-0.92%</t>
+          <t>+2.37%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>538</v>
+        <v>779</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.93%345,000</t>
+          <t>0.95%252,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.95%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>345000</v>
+        <v>252000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:40</t>
+          <t>2026-09-29 22:54:50</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,38 +2883,38 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>3293鈊象</t>
+          <t>3044健鼎</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+4.39%761</t>
+          <t>-3.16%521</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+4.39%</t>
+          <t>-3.16%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>761</v>
+        <v>521</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.91%252,000</t>
+          <t>0.92%345,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.92%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>252000</v>
+        <v>345000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:40</t>
+          <t>2026-09-29 22:54:50</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,38 +2944,38 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>3264欣銓</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-2.38%246</t>
+          <t>-3.6%6020</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-2.38%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>246</v>
+        <v>6020</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.81%650,000</t>
+          <t>0.80%26,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.80%</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>650000</v>
+        <v>26000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:40</t>
+          <t>2026-09-29 22:54:50</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,38 +3005,38 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>3264欣銓</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+0.89%6245</t>
+          <t>-1.83%241.5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+0.89%</t>
+          <t>-1.83%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>6245</v>
+        <v>241.5</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.80%26,000</t>
+          <t>0.79%650,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.79%</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>26000</v>
+        <v>650000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:40</t>
+          <t>2026-09-29 22:54:50</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,38 +3066,38 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>3529力旺</t>
+          <t>4958臻鼎-KY</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-2.27%3230</t>
+          <t>+4.84%498.5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-2.27%</t>
+          <t>+4.84%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>3230</v>
+        <v>498.5</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.72%44,000</t>
+          <t>0.71%302,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.71%</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>44000</v>
+        <v>302000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:40</t>
+          <t>2026-09-29 22:54:50</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,38 +3127,38 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>4958臻鼎-KY</t>
+          <t>3529力旺</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+0.53%475.5</t>
+          <t>+2.32%3305</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>+2.32%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>475.5</v>
+        <v>3305</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.71%302,000</t>
+          <t>0.70%44,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>0.70%</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>302000</v>
+        <v>44000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:40</t>
+          <t>2026-09-29 22:54:50</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,25 +3193,25 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-2.69%2530</t>
+          <t>-0.59%2515</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-2.69%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>2530</v>
+        <v>2515</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.70%54,000</t>
+          <t>0.68%54,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.68%</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:41</t>
+          <t>2026-09-29 22:54:52</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,16 +3254,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0%2340</t>
+          <t>+4.49%2445</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+4.49%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>2340</v>
+        <v>2445</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:41</t>
+          <t>2026-09-29 22:54:52</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,25 +3315,25 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-3.4%497.5</t>
+          <t>-1.11%492</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-1.11%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>497.5</v>
+        <v>492</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.46%182,000</t>
+          <t>0.45%182,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:41</t>
+          <t>2026-09-29 22:54:52</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,16 +3376,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+0.56%897</t>
+          <t>-2.23%877</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+0.56%</t>
+          <t>-2.23%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>897</v>
+        <v>877</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:41</t>
+          <t>2026-09-29 22:54:52</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,16 +3437,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+0.99%1530</t>
+          <t>-1.96%1500</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>-1.96%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1530</v>
+        <v>1500</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:41</t>
+          <t>2026-09-29 22:54:52</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0%1690</t>
+          <t>+1.18%1710</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+1.18%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1690</v>
+        <v>1710</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-09-29_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:48</t>
+          <t>2026-09-29 23:05:18</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:48</t>
+          <t>2026-09-29 23:05:18</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:48</t>
+          <t>2026-09-29 23:05:18</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:48</t>
+          <t>2026-09-29 23:05:18</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:48</t>
+          <t>2026-09-29 23:05:18</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:48</t>
+          <t>2026-09-29 23:05:18</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:48</t>
+          <t>2026-09-29 23:05:18</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:48</t>
+          <t>2026-09-29 23:05:18</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:48</t>
+          <t>2026-09-29 23:05:18</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:48</t>
+          <t>2026-09-29 23:05:18</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:48</t>
+          <t>2026-09-29 23:05:18</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:48</t>
+          <t>2026-09-29 23:05:18</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:48</t>
+          <t>2026-09-29 23:05:18</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:48</t>
+          <t>2026-09-29 23:05:18</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:48</t>
+          <t>2026-09-29 23:05:18</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:49</t>
+          <t>2026-09-29 23:05:19</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:49</t>
+          <t>2026-09-29 23:05:19</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:49</t>
+          <t>2026-09-29 23:05:19</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:49</t>
+          <t>2026-09-29 23:05:19</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:49</t>
+          <t>2026-09-29 23:05:19</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:49</t>
+          <t>2026-09-29 23:05:19</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:49</t>
+          <t>2026-09-29 23:05:19</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:49</t>
+          <t>2026-09-29 23:05:19</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:49</t>
+          <t>2026-09-29 23:05:19</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:49</t>
+          <t>2026-09-29 23:05:19</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:49</t>
+          <t>2026-09-29 23:05:19</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:49</t>
+          <t>2026-09-29 23:05:19</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:49</t>
+          <t>2026-09-29 23:05:19</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:49</t>
+          <t>2026-09-29 23:05:19</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:49</t>
+          <t>2026-09-29 23:05:19</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:50</t>
+          <t>2026-09-29 23:05:20</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:50</t>
+          <t>2026-09-29 23:05:20</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:50</t>
+          <t>2026-09-29 23:05:20</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:50</t>
+          <t>2026-09-29 23:05:20</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:50</t>
+          <t>2026-09-29 23:05:20</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:50</t>
+          <t>2026-09-29 23:05:20</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:50</t>
+          <t>2026-09-29 23:05:20</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:50</t>
+          <t>2026-09-29 23:05:20</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:50</t>
+          <t>2026-09-29 23:05:20</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:50</t>
+          <t>2026-09-29 23:05:20</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:50</t>
+          <t>2026-09-29 23:05:20</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:50</t>
+          <t>2026-09-29 23:05:20</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:50</t>
+          <t>2026-09-29 23:05:20</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:50</t>
+          <t>2026-09-29 23:05:20</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:50</t>
+          <t>2026-09-29 23:05:20</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:52</t>
+          <t>2026-09-29 23:05:21</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:52</t>
+          <t>2026-09-29 23:05:21</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:52</t>
+          <t>2026-09-29 23:05:21</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:52</t>
+          <t>2026-09-29 23:05:21</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:52</t>
+          <t>2026-09-29 23:05:21</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-29_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:18</t>
+          <t>2026-09-29 23:50:25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:18</t>
+          <t>2026-09-29 23:50:25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:18</t>
+          <t>2026-09-29 23:50:25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:18</t>
+          <t>2026-09-29 23:50:25</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:18</t>
+          <t>2026-09-29 23:50:25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:18</t>
+          <t>2026-09-29 23:50:25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:18</t>
+          <t>2026-09-29 23:50:25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:18</t>
+          <t>2026-09-29 23:50:25</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:18</t>
+          <t>2026-09-29 23:50:25</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:18</t>
+          <t>2026-09-29 23:50:25</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:18</t>
+          <t>2026-09-29 23:50:25</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:18</t>
+          <t>2026-09-29 23:50:25</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:18</t>
+          <t>2026-09-29 23:50:25</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:18</t>
+          <t>2026-09-29 23:50:25</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:18</t>
+          <t>2026-09-29 23:50:25</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:19</t>
+          <t>2026-09-29 23:50:26</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:19</t>
+          <t>2026-09-29 23:50:26</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:19</t>
+          <t>2026-09-29 23:50:26</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:19</t>
+          <t>2026-09-29 23:50:26</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:19</t>
+          <t>2026-09-29 23:50:26</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:19</t>
+          <t>2026-09-29 23:50:26</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:19</t>
+          <t>2026-09-29 23:50:26</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:19</t>
+          <t>2026-09-29 23:50:26</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:19</t>
+          <t>2026-09-29 23:50:26</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:19</t>
+          <t>2026-09-29 23:50:26</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:19</t>
+          <t>2026-09-29 23:50:26</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:19</t>
+          <t>2026-09-29 23:50:26</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:19</t>
+          <t>2026-09-29 23:50:26</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:19</t>
+          <t>2026-09-29 23:50:26</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:19</t>
+          <t>2026-09-29 23:50:26</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:20</t>
+          <t>2026-09-29 23:50:27</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:20</t>
+          <t>2026-09-29 23:50:27</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:20</t>
+          <t>2026-09-29 23:50:27</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:20</t>
+          <t>2026-09-29 23:50:27</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:20</t>
+          <t>2026-09-29 23:50:27</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:20</t>
+          <t>2026-09-29 23:50:27</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:20</t>
+          <t>2026-09-29 23:50:27</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:20</t>
+          <t>2026-09-29 23:50:27</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:20</t>
+          <t>2026-09-29 23:50:27</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:20</t>
+          <t>2026-09-29 23:50:27</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:20</t>
+          <t>2026-09-29 23:50:27</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:20</t>
+          <t>2026-09-29 23:50:27</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:20</t>
+          <t>2026-09-29 23:50:27</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:20</t>
+          <t>2026-09-29 23:50:27</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:20</t>
+          <t>2026-09-29 23:50:27</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:21</t>
+          <t>2026-09-29 23:50:29</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:21</t>
+          <t>2026-09-29 23:50:29</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:21</t>
+          <t>2026-09-29 23:50:29</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:21</t>
+          <t>2026-09-29 23:50:29</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:21</t>
+          <t>2026-09-29 23:50:29</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
